--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50523,13 +50523,57 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2095呎 (4+房)
+$11000万
+$52,506/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1294呎 (4+房)
+$5406万
+$41,780/呎
+(26年-01月-02日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1294呎 (4+房)
+$5500万
+$42,504/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1866呎 (4+房)
+$9580万
+$51,340/呎
+(24年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1388万
@@ -50537,7 +50581,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $2009万
@@ -50545,8 +50589,8 @@
 (21年-06月-02日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 850呎 (3房)
 $3362万
@@ -50554,50 +50598,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2095呎 (4+房)
-$11000万
-$52,506/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1294呎 (4+房)
-$5406万
-$41,780/呎
-(26年-01月-02日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1294呎 (4+房)
-$5500万
-$42,504/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1866呎 (4+房)
-$9580万
-$51,340/呎
-(24年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -50655,11 +50655,62 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5422万
+$44,963/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (1房)
+$1340万
+$34,455/呎
+(21年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1993万
+$34,841/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$6600万
+$54,187/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3289万
+$39,160/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>39&amp;40</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4163万
@@ -50667,7 +50718,7 @@
 (26年-01月-12日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4278万
@@ -50675,61 +50726,10 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5422万
-$44,963/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (1房)
-$1340万
-$34,455/呎
-(21年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1993万
-$34,841/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$6600万
-$54,187/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3289万
-$39,160/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
     </row>
@@ -50787,10 +50787,40 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4222万
+$32,678/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4220万
+$32,663/呎
+(25年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5434万
@@ -50798,9 +50828,9 @@
 (21年-06月-17日)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1321万
@@ -50808,7 +50838,7 @@
 (21年-05月-01日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1822万
@@ -50816,7 +50846,7 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5288万
@@ -50824,7 +50854,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3102万
@@ -50832,36 +50862,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4222万
-$32,678/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4220万
-$32,663/呎
-(25年-03月-14日)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -50919,11 +50919,62 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5246万
+$43,537/呎
+(21年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1314万
+$34,308/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1878万
+$32,770/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5176万
+$42,500/呎
+(21年-06月-07日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3071万
+$36,560/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35&amp;36</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4570万
@@ -50931,7 +50982,7 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4335万
@@ -50939,61 +50990,10 @@
 (25年-03月-12日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5246万
-$43,537/呎
-(21年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1314万
-$34,308/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1878万
-$32,770/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5176万
-$42,500/呎
-(21年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3071万
-$36,560/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51051,11 +51051,62 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5000万
+$41,492/呎
+(23年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1292万
+$33,736/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1848万
+$32,260/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$4820万
+$39,571/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3152万
+$37,521/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32&amp;33</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr"/>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4190万
@@ -51063,7 +51114,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4133万
@@ -51071,61 +51122,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="inlineStr"/>
-      <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="inlineStr"/>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5000万
-$41,492/呎
-(23年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr"/>
-      <c r="D19" s="20" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1292万
-$33,736/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1848万
-$32,260/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$4820万
-$39,571/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3152万
-$37,521/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51315,11 +51315,62 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5018万
+$41,609/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1298万
+$33,883/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1595万
+$27,834/呎
+(24年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5000万
+$41,051/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2957万
+$35,204/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4091万
@@ -51327,7 +51378,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4039万
@@ -51335,61 +51386,10 @@
 (25年-04月-28日)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr"/>
-      <c r="F24" s="20" t="inlineStr"/>
-      <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="20" t="inlineStr"/>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5018万
-$41,609/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr"/>
-      <c r="D25" s="20" t="inlineStr"/>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1298万
-$33,883/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1595万
-$27,834/呎
-(24年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5000万
-$41,051/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2957万
-$35,204/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>
@@ -51579,11 +51579,62 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$3988万
+$33,068/呎
+(24年-02月-01日)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1236万
+$32,282/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1726万
+$30,168/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3600万
+$29,556/呎
+(24年-11月-07日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2783万
+$33,126/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23&amp;25</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4365万
@@ -51591,7 +51642,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3948万
@@ -51599,61 +51650,10 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr"/>
-      <c r="F30" s="20" t="inlineStr"/>
-      <c r="G30" s="20" t="inlineStr"/>
-      <c r="H30" s="20" t="inlineStr"/>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$3988万
-$33,068/呎
-(24年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr"/>
-      <c r="D31" s="20" t="inlineStr"/>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1236万
-$32,282/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1726万
-$30,168/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3600万
-$29,556/呎
-(24年-11月-07日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2783万
-$33,126/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50523,10 +50523,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (1房)
+$1388万
+$35,668/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$2009万
+$35,122/呎
+(21年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 850呎 (3房)
+$3362万
+$39,552/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2095呎 (4+房)
 $11000万
@@ -50534,7 +50571,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1294呎 (4+房)
 $5406万
@@ -50542,7 +50579,7 @@
 (26年-01月-02日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1294呎 (4+房)
 $5500万
@@ -50550,9 +50587,9 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 1866呎 (4+房)
 $9580万
@@ -50560,44 +50597,7 @@
 (24年-03月-27日)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (1房)
-$1388万
-$35,668/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$2009万
-$35,122/呎
-(21年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 850呎 (3房)
-$3362万
-$39,552/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -50787,11 +50787,62 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5434万
+$45,054/呎
+(21年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1321万
+$34,480/呎
+(21年-05月-01日)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1822万
+$31,803/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5288万
+$43,415/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3102万
+$36,926/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4222万
@@ -50799,7 +50850,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4220万
@@ -50807,61 +50858,10 @@
 (25年-03月-14日)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5434万
-$45,054/呎
-(21年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1321万
-$34,480/呎
-(21年-05月-01日)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1822万
-$31,803/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5288万
-$43,415/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3102万
-$36,926/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -51183,11 +51183,62 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4880万
+$40,466/呎
+(21年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr"/>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1255万
+$32,770/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1773万
+$30,935/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3992万
+$32,778/呎
+(24年-09月-25日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2867万
+$34,131/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30&amp;31</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr"/>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4278万
@@ -51195,7 +51246,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4076万
@@ -51203,61 +51254,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr"/>
-      <c r="F21" s="20" t="inlineStr"/>
-      <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="20" t="inlineStr"/>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4880万
-$40,466/呎
-(21年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr"/>
-      <c r="D22" s="20" t="inlineStr"/>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1255万
-$32,770/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1773万
-$30,935/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3992万
-$32,778/呎
-(24年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2867万
-$34,131/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51315,10 +51315,40 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4091万
+$31,666/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4039万
+$31,260/呎
+(25年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="20" t="inlineStr"/>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5018万
@@ -51326,9 +51356,9 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr"/>
-      <c r="D24" s="20" t="inlineStr"/>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1298万
@@ -51336,7 +51366,7 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1595万
@@ -51344,7 +51374,7 @@
 (24年-03月-21日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5000万
@@ -51352,7 +51382,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2957万
@@ -51360,36 +51390,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr"/>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4091万
-$31,666/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4039万
-$31,260/呎
-(25年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr"/>
-      <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50655,10 +50655,40 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>39&amp;40</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4163万
+$32,222/呎
+(26年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5422万
@@ -50666,9 +50696,9 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1340万
@@ -50676,7 +50706,7 @@
 (21年-05月-08日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1993万
@@ -50684,7 +50714,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $6600万
@@ -50692,7 +50722,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3289万
@@ -50700,36 +50730,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39&amp;40</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4163万
-$32,222/呎
-(26年-01月-12日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
     </row>
@@ -50919,10 +50919,40 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35&amp;36</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4570万
+$35,372/呎
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4335万
+$33,556/呎
+(25年-03月-12日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5246万
@@ -50930,9 +50960,9 @@
 (21年-06月-03日)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1314万
@@ -50940,7 +50970,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1878万
@@ -50948,7 +50978,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5176万
@@ -50956,7 +50986,7 @@
 (21年-06月-07日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3071万
@@ -50964,36 +50994,6 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35&amp;36</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4570万
-$35,372/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4335万
-$33,556/呎
-(25年-03月-12日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51051,10 +51051,40 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32&amp;33</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr"/>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4190万
+$32,430/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4133万
+$31,987/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5000万
@@ -51062,9 +51092,9 @@
 (23年-03月-10日)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr"/>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1292万
@@ -51072,7 +51102,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1848万
@@ -51080,7 +51110,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $4820万
@@ -51088,7 +51118,7 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3152万
@@ -51096,36 +51126,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32&amp;33</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr"/>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4190万
-$32,430/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4133万
-$31,987/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr"/>
-      <c r="F19" s="20" t="inlineStr"/>
-      <c r="G19" s="20" t="inlineStr"/>
-      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51183,10 +51183,40 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30&amp;31</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4076万
+$31,545/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4880万
@@ -51194,9 +51224,9 @@
 (21年-07月-15日)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr"/>
-      <c r="D21" s="20" t="inlineStr"/>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1255万
@@ -51204,7 +51234,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1773万
@@ -51212,7 +51242,7 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3992万
@@ -51220,7 +51250,7 @@
 (24年-09月-25日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2867万
@@ -51228,36 +51258,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30&amp;31</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4076万
-$31,545/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr"/>
-      <c r="F22" s="20" t="inlineStr"/>
-      <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51447,10 +51447,40 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26&amp;27</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4630万
+$35,836/呎
+(23年-06月-21日)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3998万
+$30,947/呎
+(24年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4840万
@@ -51458,9 +51488,9 @@
 (21年-05月-26日)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr"/>
-      <c r="D27" s="20" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1288万
@@ -51468,7 +51498,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1789万
@@ -51476,7 +51506,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3664万
@@ -51484,7 +51514,7 @@
 (24年-10月-18日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2810万
@@ -51492,36 +51522,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26&amp;27</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr"/>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4630万
-$35,836/呎
-(23年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3998万
-$30,947/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr"/>
-      <c r="F28" s="20" t="inlineStr"/>
-      <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>
@@ -51579,10 +51579,40 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23&amp;25</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4365万
+$33,786/呎
+(24年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3948万
+$30,556/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="20" t="inlineStr"/>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $3988万
@@ -51590,9 +51620,9 @@
 (24年-02月-01日)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr"/>
-      <c r="D30" s="20" t="inlineStr"/>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr"/>
+      <c r="D31" s="20" t="inlineStr"/>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1236万
@@ -51600,7 +51630,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1726万
@@ -51608,7 +51638,7 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3600万
@@ -51616,7 +51646,7 @@
 (24年-11月-07日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2783万
@@ -51624,36 +51654,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23&amp;25</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4365万
-$33,786/呎
-(24年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3948万
-$30,556/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr"/>
-      <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50523,13 +50523,57 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2095呎 (4+房)
+$11000万
+$52,506/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1294呎 (4+房)
+$5406万
+$41,780/呎
+(26年-01月-02日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1294呎 (4+房)
+$5500万
+$42,504/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1866呎 (4+房)
+$9580万
+$51,340/呎
+(24年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1388万
@@ -50537,7 +50581,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $2009万
@@ -50545,8 +50589,8 @@
 (21年-06月-02日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 850呎 (3房)
 $3362万
@@ -50554,50 +50598,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2095呎 (4+房)
-$11000万
-$52,506/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1294呎 (4+房)
-$5406万
-$41,780/呎
-(26年-01月-02日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1294呎 (4+房)
-$5500万
-$42,504/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1866呎 (4+房)
-$9580万
-$51,340/呎
-(24年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -51579,11 +51579,62 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$3988万
+$33,068/呎
+(24年-02月-01日)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1236万
+$32,282/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1726万
+$30,168/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3600万
+$29,556/呎
+(24年-11月-07日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2783万
+$33,126/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23&amp;25</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4365万
@@ -51591,7 +51642,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3948万
@@ -51599,61 +51650,10 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr"/>
-      <c r="F30" s="20" t="inlineStr"/>
-      <c r="G30" s="20" t="inlineStr"/>
-      <c r="H30" s="20" t="inlineStr"/>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$3988万
-$33,068/呎
-(24年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr"/>
-      <c r="D31" s="20" t="inlineStr"/>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1236万
-$32,282/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1726万
-$30,168/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3600万
-$29,556/呎
-(24年-11月-07日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2783万
-$33,126/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -51051,11 +51051,62 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5000万
+$41,492/呎
+(23年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1292万
+$33,736/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1848万
+$32,260/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$4820万
+$39,571/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3152万
+$37,521/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32&amp;33</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr"/>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4190万
@@ -51063,7 +51114,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4133万
@@ -51071,61 +51122,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="inlineStr"/>
-      <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="inlineStr"/>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5000万
-$41,492/呎
-(23年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr"/>
-      <c r="D19" s="20" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1292万
-$33,736/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1848万
-$32,260/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$4820万
-$39,571/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3152万
-$37,521/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51183,11 +51183,62 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4880万
+$40,466/呎
+(21年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr"/>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1255万
+$32,770/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1773万
+$30,935/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3992万
+$32,778/呎
+(24年-09月-25日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2867万
+$34,131/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30&amp;31</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr"/>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4278万
@@ -51195,7 +51246,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4076万
@@ -51203,61 +51254,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr"/>
-      <c r="F21" s="20" t="inlineStr"/>
-      <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="20" t="inlineStr"/>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4880万
-$40,466/呎
-(21年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr"/>
-      <c r="D22" s="20" t="inlineStr"/>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1255万
-$32,770/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1773万
-$30,935/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3992万
-$32,778/呎
-(24年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2867万
-$34,131/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51315,11 +51315,62 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5018万
+$41,609/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1298万
+$33,883/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1595万
+$27,834/呎
+(24年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5000万
+$41,051/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2957万
+$35,204/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4091万
@@ -51327,7 +51378,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4039万
@@ -51335,61 +51386,10 @@
 (25年-04月-28日)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr"/>
-      <c r="F24" s="20" t="inlineStr"/>
-      <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="20" t="inlineStr"/>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5018万
-$41,609/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr"/>
-      <c r="D25" s="20" t="inlineStr"/>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1298万
-$33,883/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1595万
-$27,834/呎
-(24年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5000万
-$41,051/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2957万
-$35,204/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50523,10 +50523,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (1房)
+$1388万
+$35,668/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$2009万
+$35,122/呎
+(21年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 850呎 (3房)
+$3362万
+$39,552/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2095呎 (4+房)
 $11000万
@@ -50534,7 +50571,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1294呎 (4+房)
 $5406万
@@ -50542,7 +50579,7 @@
 (26年-01月-02日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1294呎 (4+房)
 $5500万
@@ -50550,9 +50587,9 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 1866呎 (4+房)
 $9580万
@@ -50560,44 +50597,7 @@
 (24年-03月-27日)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (1房)
-$1388万
-$35,668/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$2009万
-$35,122/呎
-(21年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 850呎 (3房)
-$3362万
-$39,552/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -51315,10 +51315,40 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4091万
+$31,666/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4039万
+$31,260/呎
+(25年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="20" t="inlineStr"/>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5018万
@@ -51326,9 +51356,9 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr"/>
-      <c r="D24" s="20" t="inlineStr"/>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1298万
@@ -51336,7 +51366,7 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1595万
@@ -51344,7 +51374,7 @@
 (24年-03月-21日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5000万
@@ -51352,7 +51382,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2957万
@@ -51360,36 +51390,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr"/>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4091万
-$31,666/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4039万
-$31,260/呎
-(25年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr"/>
-      <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>
@@ -51579,10 +51579,40 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23&amp;25</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4365万
+$33,786/呎
+(24年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3948万
+$30,556/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="20" t="inlineStr"/>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $3988万
@@ -51590,9 +51620,9 @@
 (24年-02月-01日)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr"/>
-      <c r="D30" s="20" t="inlineStr"/>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr"/>
+      <c r="D31" s="20" t="inlineStr"/>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1236万
@@ -51600,7 +51630,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1726万
@@ -51608,7 +51638,7 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3600万
@@ -51616,7 +51646,7 @@
 (24年-11月-07日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2783万
@@ -51624,36 +51654,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23&amp;25</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4365万
-$33,786/呎
-(24年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3948万
-$30,556/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr"/>
-      <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50919,11 +50919,62 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5246万
+$43,537/呎
+(21年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1314万
+$34,308/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1878万
+$32,770/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5176万
+$42,500/呎
+(21年-06月-07日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3071万
+$36,560/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35&amp;36</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4570万
@@ -50931,7 +50982,7 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4335万
@@ -50939,61 +50990,10 @@
 (25年-03月-12日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5246万
-$43,537/呎
-(21年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1314万
-$34,308/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1878万
-$32,770/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5176万
-$42,500/呎
-(21年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3071万
-$36,560/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51315,11 +51315,62 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5018万
+$41,609/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1298万
+$33,883/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1595万
+$27,834/呎
+(24年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5000万
+$41,051/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2957万
+$35,204/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4091万
@@ -51327,7 +51378,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4039万
@@ -51335,61 +51386,10 @@
 (25年-04月-28日)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr"/>
-      <c r="F24" s="20" t="inlineStr"/>
-      <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="20" t="inlineStr"/>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5018万
-$41,609/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr"/>
-      <c r="D25" s="20" t="inlineStr"/>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1298万
-$33,883/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1595万
-$27,834/呎
-(24年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5000万
-$41,051/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2957万
-$35,204/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>
@@ -51579,11 +51579,62 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$3988万
+$33,068/呎
+(24年-02月-01日)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1236万
+$32,282/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1726万
+$30,168/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3600万
+$29,556/呎
+(24年-11月-07日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2783万
+$33,126/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23&amp;25</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4365万
@@ -51591,7 +51642,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3948万
@@ -51599,61 +51650,10 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr"/>
-      <c r="F30" s="20" t="inlineStr"/>
-      <c r="G30" s="20" t="inlineStr"/>
-      <c r="H30" s="20" t="inlineStr"/>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$3988万
-$33,068/呎
-(24年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr"/>
-      <c r="D31" s="20" t="inlineStr"/>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1236万
-$32,282/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1726万
-$30,168/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3600万
-$29,556/呎
-(24年-11月-07日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2783万
-$33,126/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -13158,7 +13158,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>40561000</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>35737</v>
+        <v>35705</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>40561000</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>35737</v>
+        <v>35705</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -50523,13 +50523,57 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2095呎 (4+房)
+$11000万
+$52,506/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1294呎 (4+房)
+$5406万
+$41,780/呎
+(26年-01月-02日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1294呎 (4+房)
+$5500万
+$42,504/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1866呎 (4+房)
+$9580万
+$51,340/呎
+(24年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1388万
@@ -50537,7 +50581,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $2009万
@@ -50545,8 +50589,8 @@
 (21年-06月-02日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 850呎 (3房)
 $3362万
@@ -50554,50 +50598,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2095呎 (4+房)
-$11000万
-$52,506/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1294呎 (4+房)
-$5406万
-$41,780/呎
-(26年-01月-02日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1294呎 (4+房)
-$5500万
-$42,504/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1866呎 (4+房)
-$9580万
-$51,340/呎
-(24年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -50787,10 +50787,40 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4222万
+$32,678/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4220万
+$32,663/呎
+(25年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5434万
@@ -50798,9 +50828,9 @@
 (21年-06月-17日)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1321万
@@ -50808,7 +50838,7 @@
 (21年-05月-01日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1822万
@@ -50816,7 +50846,7 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5288万
@@ -50824,7 +50854,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3102万
@@ -50832,36 +50862,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4222万
-$32,678/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4220万
-$32,663/呎
-(25年-03月-14日)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -50919,10 +50919,40 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35&amp;36</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4570万
+$35,372/呎
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4335万
+$33,556/呎
+(25年-03月-12日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5246万
@@ -50930,9 +50960,9 @@
 (21年-06月-03日)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1314万
@@ -50940,7 +50970,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1878万
@@ -50948,7 +50978,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5176万
@@ -50956,7 +50986,7 @@
 (21年-06月-07日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3071万
@@ -50964,36 +50994,6 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35&amp;36</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4570万
-$35,372/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4335万
-$33,556/呎
-(25年-03月-12日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51183,10 +51183,40 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30&amp;31</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4076万
+$31,545/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4880万
@@ -51194,9 +51224,9 @@
 (21年-07月-15日)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr"/>
-      <c r="D21" s="20" t="inlineStr"/>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1255万
@@ -51204,7 +51234,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1773万
@@ -51212,7 +51242,7 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3992万
@@ -51220,7 +51250,7 @@
 (24年-09月-25日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2867万
@@ -51228,36 +51258,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30&amp;31</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4076万
-$31,545/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr"/>
-      <c r="F22" s="20" t="inlineStr"/>
-      <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51315,10 +51315,40 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4091万
+$31,666/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4039万
+$31,260/呎
+(25年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="20" t="inlineStr"/>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5018万
@@ -51326,9 +51356,9 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr"/>
-      <c r="D24" s="20" t="inlineStr"/>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1298万
@@ -51336,7 +51366,7 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1595万
@@ -51344,7 +51374,7 @@
 (24年-03月-21日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5000万
@@ -51352,7 +51382,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2957万
@@ -51360,36 +51390,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr"/>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4091万
-$31,666/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4039万
-$31,260/呎
-(25年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr"/>
-      <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>
@@ -51447,11 +51447,62 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4840万
+$40,137/呎
+(21年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1288万
+$33,632/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1789万
+$31,220/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3664万
+$30,079/呎
+(24年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2810万
+$33,457/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26&amp;27</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr"/>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4630万
@@ -51459,7 +51510,7 @@
 (23年-06月-21日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3998万
@@ -51467,61 +51518,10 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr"/>
-      <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="inlineStr"/>
-      <c r="H27" s="20" t="inlineStr"/>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4840万
-$40,137/呎
-(21年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr"/>
-      <c r="D28" s="20" t="inlineStr"/>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1288万
-$33,632/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1789万
-$31,220/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3664万
-$30,079/呎
-(24年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2810万
-$33,457/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>
@@ -52441,9 +52441,9 @@
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>A | 1135呎 (4+房)
+          <t>A | 1136呎 (4+房)
 $4056万
-$35,737/呎
+$35,705/呎
 (21年-06月-04日)</t>
         </is>
       </c>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50655,11 +50655,62 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5422万
+$44,963/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (1房)
+$1340万
+$34,455/呎
+(21年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1993万
+$34,841/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$6600万
+$54,187/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3289万
+$39,160/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>39&amp;40</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4163万
@@ -50667,7 +50718,7 @@
 (26年-01月-12日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4278万
@@ -50675,61 +50726,10 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5422万
-$44,963/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (1房)
-$1340万
-$34,455/呎
-(21年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1993万
-$34,841/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$6600万
-$54,187/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3289万
-$39,160/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
     </row>
@@ -50787,11 +50787,62 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5434万
+$45,054/呎
+(21年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1321万
+$34,480/呎
+(21年-05月-01日)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1822万
+$31,803/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5288万
+$43,415/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3102万
+$36,926/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4222万
@@ -50799,7 +50850,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4220万
@@ -50807,61 +50858,10 @@
 (25年-03月-14日)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5434万
-$45,054/呎
-(21年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1321万
-$34,480/呎
-(21年-05月-01日)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1822万
-$31,803/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5288万
-$43,415/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3102万
-$36,926/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -51051,10 +51051,40 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32&amp;33</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr"/>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4190万
+$32,430/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4133万
+$31,987/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5000万
@@ -51062,9 +51092,9 @@
 (23年-03月-10日)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr"/>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1292万
@@ -51072,7 +51102,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1848万
@@ -51080,7 +51110,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $4820万
@@ -51088,7 +51118,7 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3152万
@@ -51096,36 +51126,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32&amp;33</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr"/>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4190万
-$32,430/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4133万
-$31,987/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr"/>
-      <c r="F19" s="20" t="inlineStr"/>
-      <c r="G19" s="20" t="inlineStr"/>
-      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51579,10 +51579,40 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23&amp;25</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4365万
+$33,786/呎
+(24年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3948万
+$30,556/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="20" t="inlineStr"/>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $3988万
@@ -51590,9 +51620,9 @@
 (24年-02月-01日)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr"/>
-      <c r="D30" s="20" t="inlineStr"/>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr"/>
+      <c r="D31" s="20" t="inlineStr"/>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1236万
@@ -51600,7 +51630,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1726万
@@ -51608,7 +51638,7 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3600万
@@ -51616,7 +51646,7 @@
 (24年-11月-07日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2783万
@@ -51624,36 +51654,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23&amp;25</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4365万
-$33,786/呎
-(24年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3948万
-$30,556/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr"/>
-      <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50523,10 +50523,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (1房)
+$1388万
+$35,668/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$2009万
+$35,122/呎
+(21年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 850呎 (3房)
+$3362万
+$39,552/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2095呎 (4+房)
 $11000万
@@ -50534,7 +50571,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1294呎 (4+房)
 $5406万
@@ -50542,7 +50579,7 @@
 (26年-01月-02日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1294呎 (4+房)
 $5500万
@@ -50550,9 +50587,9 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 1866呎 (4+房)
 $9580万
@@ -50560,44 +50597,7 @@
 (24年-03月-27日)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (1房)
-$1388万
-$35,668/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$2009万
-$35,122/呎
-(21年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 850呎 (3房)
-$3362万
-$39,552/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -51051,11 +51051,62 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5000万
+$41,492/呎
+(23年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1292万
+$33,736/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1848万
+$32,260/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$4820万
+$39,571/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3152万
+$37,521/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32&amp;33</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr"/>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4190万
@@ -51063,7 +51114,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4133万
@@ -51071,61 +51122,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="inlineStr"/>
-      <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="inlineStr"/>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5000万
-$41,492/呎
-(23年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr"/>
-      <c r="D19" s="20" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1292万
-$33,736/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1848万
-$32,260/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$4820万
-$39,571/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3152万
-$37,521/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51315,11 +51315,62 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5018万
+$41,609/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1298万
+$33,883/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1595万
+$27,834/呎
+(24年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5000万
+$41,051/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2957万
+$35,204/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4091万
@@ -51327,7 +51378,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4039万
@@ -51335,61 +51386,10 @@
 (25年-04月-28日)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr"/>
-      <c r="F24" s="20" t="inlineStr"/>
-      <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="20" t="inlineStr"/>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5018万
-$41,609/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr"/>
-      <c r="D25" s="20" t="inlineStr"/>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1298万
-$33,883/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1595万
-$27,834/呎
-(24年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5000万
-$41,051/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2957万
-$35,204/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>
@@ -51447,10 +51447,40 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26&amp;27</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4630万
+$35,836/呎
+(23年-06月-21日)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3998万
+$30,947/呎
+(24年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4840万
@@ -51458,9 +51488,9 @@
 (21年-05月-26日)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr"/>
-      <c r="D27" s="20" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1288万
@@ -51468,7 +51498,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1789万
@@ -51476,7 +51506,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3664万
@@ -51484,7 +51514,7 @@
 (24年-10月-18日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2810万
@@ -51492,36 +51522,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26&amp;27</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr"/>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4630万
-$35,836/呎
-(23年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3998万
-$30,947/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr"/>
-      <c r="F28" s="20" t="inlineStr"/>
-      <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>
@@ -51579,11 +51579,62 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$3988万
+$33,068/呎
+(24年-02月-01日)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1236万
+$32,282/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1726万
+$30,168/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3600万
+$29,556/呎
+(24年-11月-07日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2783万
+$33,126/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23&amp;25</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4365万
@@ -51591,7 +51642,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3948万
@@ -51599,61 +51650,10 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr"/>
-      <c r="F30" s="20" t="inlineStr"/>
-      <c r="G30" s="20" t="inlineStr"/>
-      <c r="H30" s="20" t="inlineStr"/>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$3988万
-$33,068/呎
-(24年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr"/>
-      <c r="D31" s="20" t="inlineStr"/>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1236万
-$32,282/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1726万
-$30,168/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3600万
-$29,556/呎
-(24年-11月-07日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2783万
-$33,126/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50787,10 +50787,40 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4222万
+$32,678/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4220万
+$32,663/呎
+(25年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5434万
@@ -50798,9 +50828,9 @@
 (21年-06月-17日)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1321万
@@ -50808,7 +50838,7 @@
 (21年-05月-01日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1822万
@@ -50816,7 +50846,7 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5288万
@@ -50824,7 +50854,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3102万
@@ -50832,36 +50862,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4222万
-$32,678/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4220万
-$32,663/呎
-(25年-03月-14日)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -51051,10 +51051,40 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32&amp;33</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr"/>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4190万
+$32,430/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4133万
+$31,987/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5000万
@@ -51062,9 +51092,9 @@
 (23年-03月-10日)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr"/>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1292万
@@ -51072,7 +51102,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1848万
@@ -51080,7 +51110,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $4820万
@@ -51088,7 +51118,7 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3152万
@@ -51096,36 +51126,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32&amp;33</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr"/>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4190万
-$32,430/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4133万
-$31,987/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr"/>
-      <c r="F19" s="20" t="inlineStr"/>
-      <c r="G19" s="20" t="inlineStr"/>
-      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51183,11 +51183,62 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4880万
+$40,466/呎
+(21年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr"/>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1255万
+$32,770/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1773万
+$30,935/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3992万
+$32,778/呎
+(24年-09月-25日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2867万
+$34,131/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30&amp;31</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr"/>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4278万
@@ -51195,7 +51246,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4076万
@@ -51203,61 +51254,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr"/>
-      <c r="F21" s="20" t="inlineStr"/>
-      <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="20" t="inlineStr"/>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4880万
-$40,466/呎
-(21年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr"/>
-      <c r="D22" s="20" t="inlineStr"/>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1255万
-$32,770/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1773万
-$30,935/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3992万
-$32,778/呎
-(24年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2867万
-$34,131/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51447,11 +51447,62 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4840万
+$40,137/呎
+(21年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1288万
+$33,632/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1789万
+$31,220/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3664万
+$30,079/呎
+(24年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2810万
+$33,457/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26&amp;27</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr"/>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4630万
@@ -51459,7 +51510,7 @@
 (23年-06月-21日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3998万
@@ -51467,61 +51518,10 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr"/>
-      <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="inlineStr"/>
-      <c r="H27" s="20" t="inlineStr"/>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4840万
-$40,137/呎
-(21年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr"/>
-      <c r="D28" s="20" t="inlineStr"/>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1288万
-$33,632/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1789万
-$31,220/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3664万
-$30,079/呎
-(24年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2810万
-$33,457/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>
@@ -51579,10 +51579,40 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23&amp;25</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4365万
+$33,786/呎
+(24年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3948万
+$30,556/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="20" t="inlineStr"/>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $3988万
@@ -51590,9 +51620,9 @@
 (24年-02月-01日)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr"/>
-      <c r="D30" s="20" t="inlineStr"/>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr"/>
+      <c r="D31" s="20" t="inlineStr"/>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1236万
@@ -51600,7 +51630,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1726万
@@ -51608,7 +51638,7 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3600万
@@ -51616,7 +51646,7 @@
 (24年-11月-07日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2783万
@@ -51624,36 +51654,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23&amp;25</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4365万
-$33,786/呎
-(24年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3948万
-$30,556/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr"/>
-      <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50523,13 +50523,57 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2095呎 (4+房)
+$11000万
+$52,506/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1294呎 (4+房)
+$5406万
+$41,780/呎
+(26年-01月-02日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1294呎 (4+房)
+$5500万
+$42,504/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1866呎 (4+房)
+$9580万
+$51,340/呎
+(24年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1388万
@@ -50537,7 +50581,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $2009万
@@ -50545,8 +50589,8 @@
 (21年-06月-02日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 850呎 (3房)
 $3362万
@@ -50554,50 +50598,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2095呎 (4+房)
-$11000万
-$52,506/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1294呎 (4+房)
-$5406万
-$41,780/呎
-(26年-01月-02日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1294呎 (4+房)
-$5500万
-$42,504/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1866呎 (4+房)
-$9580万
-$51,340/呎
-(24年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -50787,11 +50787,62 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5434万
+$45,054/呎
+(21年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1321万
+$34,480/呎
+(21年-05月-01日)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1822万
+$31,803/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5288万
+$43,415/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3102万
+$36,926/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4222万
@@ -50799,7 +50850,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4220万
@@ -50807,61 +50858,10 @@
 (25年-03月-14日)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5434万
-$45,054/呎
-(21年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1321万
-$34,480/呎
-(21年-05月-01日)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1822万
-$31,803/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5288万
-$43,415/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3102万
-$36,926/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -50919,11 +50919,62 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5246万
+$43,537/呎
+(21年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1314万
+$34,308/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1878万
+$32,770/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5176万
+$42,500/呎
+(21年-06月-07日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3071万
+$36,560/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35&amp;36</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4570万
@@ -50931,7 +50982,7 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4335万
@@ -50939,61 +50990,10 @@
 (25年-03月-12日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5246万
-$43,537/呎
-(21年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1314万
-$34,308/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1878万
-$32,770/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5176万
-$42,500/呎
-(21年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3071万
-$36,560/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51051,11 +51051,62 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5000万
+$41,492/呎
+(23年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1292万
+$33,736/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1848万
+$32,260/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$4820万
+$39,571/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3152万
+$37,521/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32&amp;33</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr"/>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4190万
@@ -51063,7 +51114,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4133万
@@ -51071,61 +51122,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="inlineStr"/>
-      <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="inlineStr"/>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5000万
-$41,492/呎
-(23年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr"/>
-      <c r="D19" s="20" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1292万
-$33,736/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1848万
-$32,260/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$4820万
-$39,571/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3152万
-$37,521/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51183,10 +51183,40 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30&amp;31</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4076万
+$31,545/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4880万
@@ -51194,9 +51224,9 @@
 (21年-07月-15日)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr"/>
-      <c r="D21" s="20" t="inlineStr"/>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1255万
@@ -51204,7 +51234,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1773万
@@ -51212,7 +51242,7 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3992万
@@ -51220,7 +51250,7 @@
 (24年-09月-25日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2867万
@@ -51228,36 +51258,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30&amp;31</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4076万
-$31,545/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr"/>
-      <c r="F22" s="20" t="inlineStr"/>
-      <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51447,10 +51447,40 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26&amp;27</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4630万
+$35,836/呎
+(23年-06月-21日)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3998万
+$30,947/呎
+(24年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4840万
@@ -51458,9 +51488,9 @@
 (21年-05月-26日)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr"/>
-      <c r="D27" s="20" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1288万
@@ -51468,7 +51498,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1789万
@@ -51476,7 +51506,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3664万
@@ -51484,7 +51514,7 @@
 (24年-10月-18日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2810万
@@ -51492,36 +51522,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26&amp;27</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr"/>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4630万
-$35,836/呎
-(23年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3998万
-$30,947/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr"/>
-      <c r="F28" s="20" t="inlineStr"/>
-      <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>
@@ -51579,11 +51579,62 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$3988万
+$33,068/呎
+(24年-02月-01日)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1236万
+$32,282/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1726万
+$30,168/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3600万
+$29,556/呎
+(24年-11月-07日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2783万
+$33,126/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23&amp;25</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4365万
@@ -51591,7 +51642,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3948万
@@ -51599,61 +51650,10 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr"/>
-      <c r="F30" s="20" t="inlineStr"/>
-      <c r="G30" s="20" t="inlineStr"/>
-      <c r="H30" s="20" t="inlineStr"/>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$3988万
-$33,068/呎
-(24年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr"/>
-      <c r="D31" s="20" t="inlineStr"/>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1236万
-$32,282/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1726万
-$30,168/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3600万
-$29,556/呎
-(24年-11月-07日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2783万
-$33,126/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -50787,10 +50787,40 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4222万
+$32,678/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4220万
+$32,663/呎
+(25年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5434万
@@ -50798,9 +50828,9 @@
 (21年-06月-17日)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1321万
@@ -50808,7 +50838,7 @@
 (21年-05月-01日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1822万
@@ -50816,7 +50846,7 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5288万
@@ -50824,7 +50854,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3102万
@@ -50832,36 +50862,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4222万
-$32,678/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4220万
-$32,663/呎
-(25年-03月-14日)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -51051,10 +51051,40 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32&amp;33</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr"/>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4190万
+$32,430/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4133万
+$31,987/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5000万
@@ -51062,9 +51092,9 @@
 (23年-03月-10日)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr"/>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1292万
@@ -51072,7 +51102,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1848万
@@ -51080,7 +51110,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $4820万
@@ -51088,7 +51118,7 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3152万
@@ -51096,36 +51126,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32&amp;33</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr"/>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4190万
-$32,430/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4133万
-$31,987/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr"/>
-      <c r="F19" s="20" t="inlineStr"/>
-      <c r="G19" s="20" t="inlineStr"/>
-      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51183,11 +51183,62 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4880万
+$40,466/呎
+(21年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr"/>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1255万
+$32,770/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1773万
+$30,935/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3992万
+$32,778/呎
+(24年-09月-25日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2867万
+$34,131/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30&amp;31</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr"/>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4278万
@@ -51195,7 +51246,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4076万
@@ -51203,61 +51254,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr"/>
-      <c r="F21" s="20" t="inlineStr"/>
-      <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="20" t="inlineStr"/>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4880万
-$40,466/呎
-(21年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr"/>
-      <c r="D22" s="20" t="inlineStr"/>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1255万
-$32,770/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1773万
-$30,935/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3992万
-$32,778/呎
-(24年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2867万
-$34,131/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51315,10 +51315,40 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4091万
+$31,666/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4039万
+$31,260/呎
+(25年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="20" t="inlineStr"/>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5018万
@@ -51326,9 +51356,9 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr"/>
-      <c r="D24" s="20" t="inlineStr"/>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1298万
@@ -51336,7 +51366,7 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1595万
@@ -51344,7 +51374,7 @@
 (24年-03月-21日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5000万
@@ -51352,7 +51382,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2957万
@@ -51360,36 +51390,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr"/>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4091万
-$31,666/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4039万
-$31,260/呎
-(25年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr"/>
-      <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>
